--- a/corrections-&-ajout-gestion-erreurs-supplémentaires/ig/StructureDefinition-as-bal-mss-per.xlsx
+++ b/corrections-&-ajout-gestion-erreurs-supplémentaires/ig/StructureDefinition-as-bal-mss-per.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:54:32+00:00</t>
+    <t>2026-06-24T13:30:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/corrections-&-ajout-gestion-erreurs-supplémentaires/ig/StructureDefinition-as-bal-mss-per.xlsx
+++ b/corrections-&-ajout-gestion-erreurs-supplémentaires/ig/StructureDefinition-as-bal-mss-per.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:30:38+00:00</t>
+    <t>2026-06-24T13:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
